--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T3_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>50</t>
+    <t>44</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -63,28 +63,28 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.460</t>
-  </si>
-  <si>
-    <t>(0.071)</t>
-  </si>
-  <si>
-    <t>0.340</t>
-  </si>
-  <si>
-    <t>(0.068)</t>
-  </si>
-  <si>
-    <t>1.000</t>
-  </si>
-  <si>
-    <t>(0.204)</t>
-  </si>
-  <si>
-    <t>0.620</t>
-  </si>
-  <si>
-    <t>(0.169)</t>
+    <t>0.523</t>
+  </si>
+  <si>
+    <t>(0.076)</t>
+  </si>
+  <si>
+    <t>0.386</t>
+  </si>
+  <si>
+    <t>(0.074)</t>
+  </si>
+  <si>
+    <t>1.136</t>
+  </si>
+  <si>
+    <t>(0.224)</t>
+  </si>
+  <si>
+    <t>0.705</t>
+  </si>
+  <si>
+    <t>(0.188)</t>
   </si>
   <si>
     <t>66</t>
@@ -123,7 +123,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -135,16 +135,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.419***</t>
-  </si>
-  <si>
-    <t>0.327***</t>
-  </si>
-  <si>
-    <t>3.394***</t>
-  </si>
-  <si>
-    <t>1.183***</t>
+    <t>0.356***</t>
+  </si>
+  <si>
+    <t>0.280***</t>
+  </si>
+  <si>
+    <t>3.258***</t>
+  </si>
+  <si>
+    <t>1.098***</t>
   </si>
 </sst>
 </file>
